--- a/PPG/Calendários.xlsx
+++ b/PPG/Calendários.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FCA05B9-363B-8F4E-9838-4DE8AAE72E2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A9A591-3325-FD4E-A411-ED7429CE067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="1100" windowWidth="27640" windowHeight="16900" xr2:uid="{46CBE343-25B5-CE4C-8D60-80361989358C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="125">
   <si>
     <t>Publicação</t>
   </si>
@@ -402,6 +402,15 @@
   </si>
   <si>
     <t>https://drive.google.com/file/d/1Rhop2NC3taxpI20i5MLce8iepFA4o2C8</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/file/d/191CAFMUVWj9Seva-EJ_Su7usKjl1FlyD</t>
+  </si>
+  <si>
+    <t>2026-2</t>
+  </si>
+  <si>
+    <t>Calendário 2026-2.pdf</t>
   </si>
 </sst>
 </file>
@@ -775,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109E75EB-4039-C840-A144-16CD29903E29}">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.83203125" style="4" bestFit="1" customWidth="1"/>
@@ -794,384 +803,396 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
-        <v>119</v>
+    <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="B8" t="s">
-        <v>62</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>63</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A23" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B25" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A27" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
-        <v>3</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A31" s="4" t="s">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>8</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C33" s="2" t="s">
         <v>86</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A12:C32">
-    <sortCondition descending="1" ref="A12:A32"/>
-    <sortCondition ref="B12:B32"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A13:C33">
+    <sortCondition descending="1" ref="A13:A33"/>
+    <sortCondition ref="B13:B33"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C32" r:id="rId1" xr:uid="{4478EA1F-9AD4-DA4B-9119-2C831F1F8BD4}"/>
-    <hyperlink ref="C31" r:id="rId2" xr:uid="{FD24F3E9-AAA7-3046-9A41-9505C64481D8}"/>
-    <hyperlink ref="C30" r:id="rId3" xr:uid="{A67528C1-56A0-ED42-A28A-0246A43E1D3B}"/>
-    <hyperlink ref="C29" r:id="rId4" xr:uid="{B5AB0C23-1D93-974D-AF84-BD3D3DD3C682}"/>
-    <hyperlink ref="C28" r:id="rId5" xr:uid="{015A2681-3AFC-8246-9C99-FDDAA0B00C5B}"/>
-    <hyperlink ref="C27" r:id="rId6" xr:uid="{39F508F7-F0D7-3345-B6B7-CF52D0C752FF}"/>
-    <hyperlink ref="C26" r:id="rId7" xr:uid="{9FE47A73-0416-AB4A-92AA-EF27CA144051}"/>
-    <hyperlink ref="C25" r:id="rId8" xr:uid="{2C01992C-1661-B24E-B5CF-1D8665C22553}"/>
-    <hyperlink ref="C24" r:id="rId9" xr:uid="{587464AD-68C9-7744-8E84-8AFF34D0DC7C}"/>
-    <hyperlink ref="C23" r:id="rId10" xr:uid="{4A7F0A41-68B2-1C48-BF59-7C91CFED65C9}"/>
-    <hyperlink ref="C22" r:id="rId11" xr:uid="{339CCE84-66D9-524D-8E2D-90284877F285}"/>
-    <hyperlink ref="C21" r:id="rId12" xr:uid="{F9BAC8F7-C414-B14A-BD95-561E46581E3F}"/>
-    <hyperlink ref="C20" r:id="rId13" xr:uid="{A363BDD0-23BB-BB47-8540-384852220723}"/>
-    <hyperlink ref="C19" r:id="rId14" xr:uid="{BA5C4821-19F6-4546-96F9-2011D11A64F2}"/>
-    <hyperlink ref="C18" r:id="rId15" xr:uid="{4D4F1292-80B0-844A-A1FD-5165E7BA05B0}"/>
-    <hyperlink ref="C17" r:id="rId16" xr:uid="{11CEC33F-B9E2-6B47-97D2-281A4F3EE9D0}"/>
-    <hyperlink ref="C16" r:id="rId17" xr:uid="{46A1B943-FC81-2A4E-B9D8-07985B667EAD}"/>
-    <hyperlink ref="C15" r:id="rId18" xr:uid="{A207F30A-27A4-F140-899A-86AC552D6C7C}"/>
-    <hyperlink ref="C14" r:id="rId19" xr:uid="{F142338F-617B-8840-B275-8EE528559E72}"/>
-    <hyperlink ref="C13" r:id="rId20" xr:uid="{79D36B25-D3A5-3A44-AD17-610F9350DB26}"/>
-    <hyperlink ref="C12" r:id="rId21" xr:uid="{4A4A09D3-6122-B245-AFA7-FFCF0A16264D}"/>
-    <hyperlink ref="C11" r:id="rId22" xr:uid="{610519A2-0258-4546-B870-E6D1F02975F7}"/>
-    <hyperlink ref="C10" r:id="rId23" xr:uid="{438E4491-7A94-EA45-B956-C5F90D658C25}"/>
-    <hyperlink ref="C9" r:id="rId24" xr:uid="{9123E330-6D61-C14D-A6E3-F856A83D143D}"/>
-    <hyperlink ref="C8" r:id="rId25" xr:uid="{AC9B1AA2-B941-8743-9807-DFBE7353DF8B}"/>
-    <hyperlink ref="C7" r:id="rId26" xr:uid="{3FBFAF46-536B-2C49-87FF-9AE407EFE774}"/>
-    <hyperlink ref="C6" r:id="rId27" xr:uid="{FBABAD5E-C8DB-BA44-9B5C-48BFFE4A4E54}"/>
-    <hyperlink ref="C5" r:id="rId28" xr:uid="{9E046ECC-2ABF-704D-A740-EDDC3E5D98E2}"/>
-    <hyperlink ref="C4" r:id="rId29" xr:uid="{E95904CC-411A-6441-98AF-39DFA5DB6ED9}"/>
-    <hyperlink ref="C3" r:id="rId30" xr:uid="{C9E075F9-472A-F340-8DE7-A75E6D80C0CA}"/>
-    <hyperlink ref="C2" r:id="rId31" xr:uid="{3392FDF9-1E19-0348-8F49-AE4DDD034657}"/>
+    <hyperlink ref="C33" r:id="rId1" xr:uid="{4478EA1F-9AD4-DA4B-9119-2C831F1F8BD4}"/>
+    <hyperlink ref="C32" r:id="rId2" xr:uid="{FD24F3E9-AAA7-3046-9A41-9505C64481D8}"/>
+    <hyperlink ref="C31" r:id="rId3" xr:uid="{A67528C1-56A0-ED42-A28A-0246A43E1D3B}"/>
+    <hyperlink ref="C30" r:id="rId4" xr:uid="{B5AB0C23-1D93-974D-AF84-BD3D3DD3C682}"/>
+    <hyperlink ref="C29" r:id="rId5" xr:uid="{015A2681-3AFC-8246-9C99-FDDAA0B00C5B}"/>
+    <hyperlink ref="C28" r:id="rId6" xr:uid="{39F508F7-F0D7-3345-B6B7-CF52D0C752FF}"/>
+    <hyperlink ref="C27" r:id="rId7" xr:uid="{9FE47A73-0416-AB4A-92AA-EF27CA144051}"/>
+    <hyperlink ref="C26" r:id="rId8" xr:uid="{2C01992C-1661-B24E-B5CF-1D8665C22553}"/>
+    <hyperlink ref="C25" r:id="rId9" xr:uid="{587464AD-68C9-7744-8E84-8AFF34D0DC7C}"/>
+    <hyperlink ref="C24" r:id="rId10" xr:uid="{4A7F0A41-68B2-1C48-BF59-7C91CFED65C9}"/>
+    <hyperlink ref="C23" r:id="rId11" xr:uid="{339CCE84-66D9-524D-8E2D-90284877F285}"/>
+    <hyperlink ref="C22" r:id="rId12" xr:uid="{F9BAC8F7-C414-B14A-BD95-561E46581E3F}"/>
+    <hyperlink ref="C21" r:id="rId13" xr:uid="{A363BDD0-23BB-BB47-8540-384852220723}"/>
+    <hyperlink ref="C20" r:id="rId14" xr:uid="{BA5C4821-19F6-4546-96F9-2011D11A64F2}"/>
+    <hyperlink ref="C19" r:id="rId15" xr:uid="{4D4F1292-80B0-844A-A1FD-5165E7BA05B0}"/>
+    <hyperlink ref="C18" r:id="rId16" xr:uid="{11CEC33F-B9E2-6B47-97D2-281A4F3EE9D0}"/>
+    <hyperlink ref="C17" r:id="rId17" xr:uid="{46A1B943-FC81-2A4E-B9D8-07985B667EAD}"/>
+    <hyperlink ref="C16" r:id="rId18" xr:uid="{A207F30A-27A4-F140-899A-86AC552D6C7C}"/>
+    <hyperlink ref="C15" r:id="rId19" xr:uid="{F142338F-617B-8840-B275-8EE528559E72}"/>
+    <hyperlink ref="C14" r:id="rId20" xr:uid="{79D36B25-D3A5-3A44-AD17-610F9350DB26}"/>
+    <hyperlink ref="C13" r:id="rId21" xr:uid="{4A4A09D3-6122-B245-AFA7-FFCF0A16264D}"/>
+    <hyperlink ref="C12" r:id="rId22" xr:uid="{610519A2-0258-4546-B870-E6D1F02975F7}"/>
+    <hyperlink ref="C11" r:id="rId23" xr:uid="{438E4491-7A94-EA45-B956-C5F90D658C25}"/>
+    <hyperlink ref="C10" r:id="rId24" xr:uid="{9123E330-6D61-C14D-A6E3-F856A83D143D}"/>
+    <hyperlink ref="C9" r:id="rId25" xr:uid="{AC9B1AA2-B941-8743-9807-DFBE7353DF8B}"/>
+    <hyperlink ref="C8" r:id="rId26" xr:uid="{3FBFAF46-536B-2C49-87FF-9AE407EFE774}"/>
+    <hyperlink ref="C7" r:id="rId27" xr:uid="{FBABAD5E-C8DB-BA44-9B5C-48BFFE4A4E54}"/>
+    <hyperlink ref="C6" r:id="rId28" xr:uid="{9E046ECC-2ABF-704D-A740-EDDC3E5D98E2}"/>
+    <hyperlink ref="C5" r:id="rId29" xr:uid="{E95904CC-411A-6441-98AF-39DFA5DB6ED9}"/>
+    <hyperlink ref="C4" r:id="rId30" xr:uid="{C9E075F9-472A-F340-8DE7-A75E6D80C0CA}"/>
+    <hyperlink ref="C3" r:id="rId31" xr:uid="{3392FDF9-1E19-0348-8F49-AE4DDD034657}"/>
+    <hyperlink ref="C2" r:id="rId32" xr:uid="{8D6CFEF9-BF7E-B641-8D34-78AFC97E61B3}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/PPG/Calendários.xlsx
+++ b/PPG/Calendários.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arthurferreira/Google Drive - arthur_sf/Observatorios/ObservatorioUNISUAM-CR/PPG/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27A9A591-3325-FD4E-A411-ED7429CE067D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2015FCA9-8B3E-064C-8FBF-4E22778516A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="1100" windowWidth="27640" windowHeight="16900" xr2:uid="{46CBE343-25B5-CE4C-8D60-80361989358C}"/>
   </bookViews>
@@ -463,12 +463,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
@@ -804,7 +805,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="5" t="s">
         <v>123</v>
       </c>
       <c r="B2" t="s">
